--- a/teste da planilha_artigo_MT.xlsx
+++ b/teste da planilha_artigo_MT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ufcatalao-my.sharepoint.com/personal/victor_souza_discente_ufcat_edu_br/Documents/Mestrado/dissertação/Dissertação/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\ic_victor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{66851749-502C-427B-92CF-675B0FA1319E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07A9C592-3E0A-4E9F-8BA7-413F57748E27}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE036AD-8F8A-4ACD-B681-557A8409063D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F469007E-D377-4415-9629-4A897BF6F5EE}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F469007E-D377-4415-9629-4A897BF6F5EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>gamma_c</t>
   </si>
@@ -56,19 +56,7 @@
     <t>a_s (m²)</t>
   </si>
   <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>G</t>
-  </si>
-  <si>
-    <t>m_g</t>
-  </si>
-  <si>
-    <t>m_q</t>
   </si>
   <si>
     <t>e_r</t>
@@ -77,46 +65,59 @@
     <t>e_s</t>
   </si>
   <si>
-    <t>m_r</t>
+    <t>d(m)</t>
   </si>
   <si>
-    <t>m_s</t>
+    <t>fator_degrad</t>
   </si>
   <si>
-    <t>f_ck</t>
+    <t>m_g (kN.m)</t>
   </si>
   <si>
-    <t>f_yk</t>
+    <t>m_q (kN.m)</t>
   </si>
   <si>
-    <t>x</t>
+    <t>f_ck (kPa)</t>
   </si>
   <si>
-    <t>d</t>
+    <t>f_yk (kPa)</t>
   </si>
   <si>
-    <t>f_cd</t>
+    <t>f_cd (kPa)</t>
   </si>
   <si>
-    <t>zeta</t>
+    <t>x (m)</t>
   </si>
   <si>
-    <t>z</t>
+    <t>m_r (kN.m)</t>
   </si>
   <si>
-    <t>aux</t>
+    <t>m_s (kN.m)</t>
   </si>
   <si>
-    <t>d(m)</t>
+    <t>nº teste</t>
+  </si>
+  <si>
+    <t>t (ano)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> taxa     degrad</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>1-t1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -136,18 +137,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -155,16 +156,160 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,269 +644,2252 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD411BC7-6A25-4281-ADE7-E0D38E637218}">
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="22" width="10.77734375" customWidth="1"/>
+    <col min="23" max="24" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="O1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="W1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="X1" s="9">
+        <v>-2.2300000000000002E-3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14">
+        <v>17</v>
+      </c>
+      <c r="D2" s="14">
+        <v>2.87</v>
+      </c>
+      <c r="E2" s="6">
+        <v>25000</v>
+      </c>
+      <c r="F2" s="6">
+        <v>500000</v>
+      </c>
+      <c r="G2" s="14">
+        <v>1</v>
+      </c>
+      <c r="H2" s="14">
+        <v>1</v>
+      </c>
+      <c r="I2" s="11">
+        <v>1</v>
+      </c>
+      <c r="J2" s="11">
+        <v>1</v>
+      </c>
+      <c r="K2" s="11">
+        <v>1</v>
+      </c>
+      <c r="L2" s="11">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M2" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="N2" s="16">
+        <f>M2*0.9</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="O2" s="17">
+        <f>E2/I2</f>
+        <v>25000</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="18">
+        <f>IF(P2=0, 1, EXP($X$1*P2))</f>
+        <v>1</v>
+      </c>
+      <c r="R2" s="19">
+        <f>0.15/100*L2*M2</f>
+        <v>8.4000000000000022E-5</v>
+      </c>
+      <c r="S2" s="19">
+        <f>((R2*F2)/(O2*L2*0.85*0.8))</f>
+        <v>1.7647058823529415E-2</v>
+      </c>
+      <c r="T2" s="17">
+        <f>(R2*F2*(N2-S2*0.5*0.8))*G2</f>
+        <v>14.823529411764712</v>
+      </c>
+      <c r="U2" s="17">
+        <f>(K2*(C2+D2))*H2</f>
+        <v>19.87</v>
+      </c>
+      <c r="V2" s="20">
+        <f>T2-U2</f>
+        <v>-5.0464705882352892</v>
+      </c>
+      <c r="W2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3" s="15">
+        <v>17.958200000000001</v>
+      </c>
+      <c r="D3" s="15">
+        <v>1.8528</v>
+      </c>
+      <c r="E3" s="13">
+        <v>34861.980000000003</v>
+      </c>
+      <c r="F3" s="13">
+        <v>574413.19999999995</v>
+      </c>
+      <c r="G3" s="15">
+        <v>1.0053668066589969</v>
+      </c>
+      <c r="H3" s="15">
+        <v>0.99567807940225062</v>
+      </c>
+      <c r="I3" s="12">
+        <v>1</v>
+      </c>
+      <c r="J3" s="12">
+        <v>1</v>
+      </c>
+      <c r="K3" s="12">
+        <v>1</v>
+      </c>
+      <c r="L3" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M3" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="N3" s="16">
+        <f t="shared" ref="N3:N29" si="0">M3*0.9</f>
+        <v>0.27</v>
+      </c>
+      <c r="O3" s="17">
+        <f t="shared" ref="O3:O29" si="1">E3/I3</f>
+        <v>34861.980000000003</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="18">
+        <f t="shared" ref="Q3:Q29" si="2">IF(P3=0, 1, EXP($X$1*P3))</f>
+        <v>1</v>
+      </c>
+      <c r="R3" s="19">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S3" s="19">
+        <f t="shared" ref="S3:S29" si="3">((R3*F3)/(O3*L3*0.85*0.8))</f>
+        <v>6.5768662546399473E-2</v>
+      </c>
+      <c r="T3" s="17">
+        <f t="shared" ref="T3" si="4">(R3*F3*(N3-S3*0.5*0.8))*G3</f>
+        <v>53.477953109647295</v>
+      </c>
+      <c r="U3" s="17">
+        <f t="shared" ref="U3:U29" si="5">(K3*(C3+D3))*H3</f>
+        <v>19.725378431037988</v>
+      </c>
+      <c r="V3" s="17">
+        <f t="shared" ref="V3:V29" si="6">T3-U3</f>
+        <v>33.752574678609307</v>
+      </c>
+      <c r="W3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B4" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4" s="15">
+        <v>17.5</v>
+      </c>
+      <c r="D4" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="E4" s="13">
+        <v>25000</v>
+      </c>
+      <c r="F4" s="13">
+        <v>500000</v>
+      </c>
+      <c r="G4" s="15">
+        <v>1.2</v>
+      </c>
+      <c r="H4" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="12">
+        <v>1</v>
+      </c>
+      <c r="J4" s="12">
+        <v>1</v>
+      </c>
+      <c r="K4" s="12">
+        <v>1</v>
+      </c>
+      <c r="L4" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M4" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="N4" s="16">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="O4" s="17">
+        <f t="shared" si="1"/>
+        <v>25000</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R4" s="19">
+        <f t="shared" ref="R4:R6" si="7">0.15/100*L4*M4</f>
+        <v>8.4000000000000022E-5</v>
+      </c>
+      <c r="S4" s="19">
+        <f t="shared" si="3"/>
+        <v>1.7647058823529415E-2</v>
+      </c>
+      <c r="T4" s="17">
+        <f>(R4*F4*(N4-S4*0.5*0.8))*G4*Q4</f>
+        <v>17.788235294117655</v>
+      </c>
+      <c r="U4" s="17">
+        <f t="shared" si="5"/>
+        <v>11.5</v>
+      </c>
+      <c r="V4" s="17">
+        <f t="shared" si="6"/>
+        <v>6.2882352941176549</v>
+      </c>
+      <c r="W4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B5" s="7">
+        <v>4</v>
+      </c>
+      <c r="C5" s="15">
+        <v>50.5</v>
+      </c>
+      <c r="D5" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="E5" s="13">
+        <v>50000</v>
+      </c>
+      <c r="F5" s="13">
+        <v>600000</v>
+      </c>
+      <c r="G5" s="15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H5" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="I5" s="12">
+        <v>1</v>
+      </c>
+      <c r="J5" s="12">
+        <v>1</v>
+      </c>
+      <c r="K5" s="12">
+        <v>1</v>
+      </c>
+      <c r="L5" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="M5" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="N5" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63</v>
+      </c>
+      <c r="O5" s="17">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R5" s="19">
+        <f t="shared" si="7"/>
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="S5" s="19">
+        <f t="shared" si="3"/>
+        <v>1.8529411764705881E-2</v>
+      </c>
+      <c r="T5" s="17">
+        <f t="shared" ref="T5:T29" si="8">(R5*F5*(N5-S5*0.5*0.8))*G5*Q5</f>
+        <v>86.290729411764715</v>
+      </c>
+      <c r="U5" s="17">
+        <f t="shared" si="5"/>
+        <v>48.800000000000004</v>
+      </c>
+      <c r="V5" s="17">
+        <f t="shared" si="6"/>
+        <v>37.490729411764711</v>
+      </c>
+      <c r="W5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B6" s="7">
+        <v>5</v>
+      </c>
+      <c r="C6" s="15">
+        <v>50.5</v>
+      </c>
+      <c r="D6" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="E6" s="13">
+        <v>50000</v>
+      </c>
+      <c r="F6" s="13">
+        <v>600000</v>
+      </c>
+      <c r="G6" s="15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H6" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="I6" s="12">
+        <v>1</v>
+      </c>
+      <c r="J6" s="12">
+        <v>1</v>
+      </c>
+      <c r="K6" s="12">
+        <v>1</v>
+      </c>
+      <c r="L6" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="M6" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="N6" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63</v>
+      </c>
+      <c r="O6" s="17">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+      <c r="P6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="18">
+        <f t="shared" si="2"/>
+        <v>0.99777248460276879</v>
+      </c>
+      <c r="R6" s="19">
+        <f t="shared" si="7"/>
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="S6" s="19">
+        <f t="shared" si="3"/>
+        <v>1.8529411764705881E-2</v>
+      </c>
+      <c r="T6" s="17">
+        <f t="shared" si="8"/>
+        <v>86.098515483361695</v>
+      </c>
+      <c r="U6" s="17">
+        <f t="shared" si="5"/>
+        <v>48.800000000000004</v>
+      </c>
+      <c r="V6" s="17">
+        <f t="shared" si="6"/>
+        <v>37.29851548336169</v>
+      </c>
+      <c r="W6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B7" s="7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="15">
+        <v>50.5</v>
+      </c>
+      <c r="D7" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="E7" s="13">
+        <v>50000</v>
+      </c>
+      <c r="F7" s="13">
+        <v>600000</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H7" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="I7" s="12">
+        <v>1</v>
+      </c>
+      <c r="J7" s="12">
+        <v>1</v>
+      </c>
+      <c r="K7" s="12">
+        <v>1</v>
+      </c>
+      <c r="L7" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="M7" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="N7" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63</v>
+      </c>
+      <c r="O7" s="17">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+      <c r="P7" s="7">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="18">
+        <f t="shared" si="2"/>
+        <v>0.97794680699710346</v>
+      </c>
+      <c r="R7" s="19">
+        <f>0.15/100*L7*M7</f>
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="S7" s="19">
+        <f t="shared" si="3"/>
+        <v>1.8529411764705881E-2</v>
+      </c>
+      <c r="T7" s="17">
+        <f t="shared" si="8"/>
+        <v>84.387743301686342</v>
+      </c>
+      <c r="U7" s="17">
+        <f t="shared" si="5"/>
+        <v>48.800000000000004</v>
+      </c>
+      <c r="V7" s="17">
+        <f t="shared" si="6"/>
+        <v>35.587743301686338</v>
+      </c>
+      <c r="W7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B8" s="7">
+        <v>7</v>
+      </c>
+      <c r="C8" s="15">
+        <v>50.5</v>
+      </c>
+      <c r="D8" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="E8" s="13">
+        <v>50000</v>
+      </c>
+      <c r="F8" s="13">
+        <v>600000</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H8" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="I8" s="12">
+        <v>1</v>
+      </c>
+      <c r="J8" s="12">
+        <v>1</v>
+      </c>
+      <c r="K8" s="12">
+        <v>1</v>
+      </c>
+      <c r="L8" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="M8" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="N8" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63</v>
+      </c>
+      <c r="O8" s="17">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+      <c r="P8" s="7">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="18">
+        <f t="shared" si="2"/>
+        <v>0.95637995731583003</v>
+      </c>
+      <c r="R8" s="19">
+        <f t="shared" ref="R8:R29" si="9">0.15/100*L8*M8</f>
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="S8" s="19">
+        <f t="shared" si="3"/>
+        <v>1.8529411764705881E-2</v>
+      </c>
+      <c r="T8" s="17">
+        <f t="shared" si="8"/>
+        <v>82.526724111575376</v>
+      </c>
+      <c r="U8" s="17">
+        <f t="shared" si="5"/>
+        <v>48.800000000000004</v>
+      </c>
+      <c r="V8" s="17">
+        <f t="shared" si="6"/>
+        <v>33.726724111575372</v>
+      </c>
+      <c r="W8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B9" s="7">
+        <v>8</v>
+      </c>
+      <c r="C9" s="15">
+        <v>50.5</v>
+      </c>
+      <c r="D9" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="E9" s="13">
+        <v>50000</v>
+      </c>
+      <c r="F9" s="13">
+        <v>600000</v>
+      </c>
+      <c r="G9" s="15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H9" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="I9" s="12">
+        <v>1</v>
+      </c>
+      <c r="J9" s="12">
+        <v>1</v>
+      </c>
+      <c r="K9" s="12">
+        <v>1</v>
+      </c>
+      <c r="L9" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="M9" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="N9" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63</v>
+      </c>
+      <c r="O9" s="17">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+      <c r="P9" s="7">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="18">
+        <f t="shared" si="2"/>
+        <v>0.9352887255330421</v>
+      </c>
+      <c r="R9" s="19">
+        <f t="shared" si="9"/>
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="S9" s="19">
+        <f t="shared" si="3"/>
+        <v>1.8529411764705881E-2</v>
+      </c>
+      <c r="T9" s="17">
+        <f t="shared" si="8"/>
+        <v>80.70674633684601</v>
+      </c>
+      <c r="U9" s="17">
+        <f t="shared" si="5"/>
+        <v>48.800000000000004</v>
+      </c>
+      <c r="V9" s="17">
+        <f t="shared" si="6"/>
+        <v>31.906746336846005</v>
+      </c>
+      <c r="W9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B10" s="7">
+        <v>9</v>
+      </c>
+      <c r="C10" s="15">
+        <v>50.5</v>
+      </c>
+      <c r="D10" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="E10" s="13">
+        <v>50000</v>
+      </c>
+      <c r="F10" s="13">
+        <v>600000</v>
+      </c>
+      <c r="G10" s="15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H10" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="I10" s="12">
+        <v>1</v>
+      </c>
+      <c r="J10" s="12">
+        <v>1</v>
+      </c>
+      <c r="K10" s="12">
+        <v>1</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="M10" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="N10" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63</v>
+      </c>
+      <c r="O10" s="17">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+      <c r="P10" s="7">
+        <v>50</v>
+      </c>
+      <c r="Q10" s="18">
+        <f t="shared" si="2"/>
+        <v>0.89449139140326783</v>
+      </c>
+      <c r="R10" s="19">
+        <f t="shared" si="9"/>
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="S10" s="19">
+        <f t="shared" si="3"/>
+        <v>1.8529411764705881E-2</v>
+      </c>
+      <c r="T10" s="17">
+        <f t="shared" si="8"/>
+        <v>77.186314616732304</v>
+      </c>
+      <c r="U10" s="17">
+        <f t="shared" si="5"/>
+        <v>48.800000000000004</v>
+      </c>
+      <c r="V10" s="17">
+        <f t="shared" si="6"/>
+        <v>28.386314616732299</v>
+      </c>
+      <c r="W10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B11" s="7">
+        <v>10</v>
+      </c>
+      <c r="C11" s="15">
+        <v>50.5</v>
+      </c>
+      <c r="D11" s="15">
+        <v>10.5</v>
+      </c>
+      <c r="E11" s="13">
+        <v>50000</v>
+      </c>
+      <c r="F11" s="13">
+        <v>600000</v>
+      </c>
+      <c r="G11" s="15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H11" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="I11" s="12">
+        <v>1</v>
+      </c>
+      <c r="J11" s="12">
+        <v>1</v>
+      </c>
+      <c r="K11" s="12">
+        <v>1</v>
+      </c>
+      <c r="L11" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="M11" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="N11" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63</v>
+      </c>
+      <c r="O11" s="17">
+        <f t="shared" si="1"/>
+        <v>50000</v>
+      </c>
+      <c r="P11" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="18">
+        <f t="shared" si="2"/>
+        <v>0.80011484929455412</v>
+      </c>
+      <c r="R11" s="19">
+        <f t="shared" si="9"/>
+        <v>2.1000000000000001E-4</v>
+      </c>
+      <c r="S11" s="19">
+        <f t="shared" si="3"/>
+        <v>1.8529411764705881E-2</v>
+      </c>
+      <c r="T11" s="17">
+        <f t="shared" si="8"/>
+        <v>69.042493958811278</v>
+      </c>
+      <c r="U11" s="17">
+        <f t="shared" si="5"/>
+        <v>48.800000000000004</v>
+      </c>
+      <c r="V11" s="17">
+        <f t="shared" si="6"/>
+        <v>20.242493958811274</v>
+      </c>
+      <c r="W11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B12" s="7">
+        <v>11</v>
+      </c>
+      <c r="C12" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D12" s="15">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="13">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="13">
+        <v>5000</v>
+      </c>
+      <c r="G12" s="15">
+        <v>2</v>
+      </c>
+      <c r="H12" s="15">
+        <v>10</v>
+      </c>
+      <c r="I12" s="12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="M12" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="N12" s="16">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+      <c r="O12" s="17">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+      <c r="P12" s="7">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="18">
+        <f t="shared" si="2"/>
+        <v>0.97794680699710346</v>
+      </c>
+      <c r="R12" s="19">
+        <f t="shared" si="9"/>
+        <v>2.2499999999999999E-4</v>
+      </c>
+      <c r="S12" s="19">
+        <f t="shared" si="3"/>
+        <v>1.1029411764705882E-3</v>
+      </c>
+      <c r="T12" s="17">
+        <f t="shared" si="8"/>
+        <v>0.98920038606291572</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="5"/>
+        <v>100000</v>
+      </c>
+      <c r="V12" s="17">
+        <f t="shared" si="6"/>
+        <v>-99999.010799613941</v>
+      </c>
+      <c r="W12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B13" s="7">
+        <v>12</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="12">
+        <v>1</v>
+      </c>
+      <c r="J13" s="12">
+        <v>1</v>
+      </c>
+      <c r="K13" s="12">
+        <v>1</v>
+      </c>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R13" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T13" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V13" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B14" s="7">
+        <v>13</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="12">
+        <v>1</v>
+      </c>
+      <c r="J14" s="12">
+        <v>1</v>
+      </c>
+      <c r="K14" s="12">
+        <v>1</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R14" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T14" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U14" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B15" s="7">
+        <v>14</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="12">
+        <v>1</v>
+      </c>
+      <c r="J15" s="12">
+        <v>1</v>
+      </c>
+      <c r="K15" s="12">
+        <v>1</v>
+      </c>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R15" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T15" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B16" s="7">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="12">
+        <v>1</v>
+      </c>
+      <c r="J16" s="12">
+        <v>1</v>
+      </c>
+      <c r="K16" s="12">
+        <v>1</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R16" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T16" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B17" s="7">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="12">
+        <v>1</v>
+      </c>
+      <c r="J17" s="12">
+        <v>1</v>
+      </c>
+      <c r="K17" s="12">
+        <v>1</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R17" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T17" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B18" s="7">
+        <v>17</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="12">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12">
+        <v>1</v>
+      </c>
+      <c r="K18" s="12">
+        <v>1</v>
+      </c>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R18" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T18" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B19" s="7">
+        <v>18</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="12">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12">
+        <v>1</v>
+      </c>
+      <c r="K19" s="12">
+        <v>1</v>
+      </c>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R19" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T19" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="7">
+        <v>19</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="12">
+        <v>1</v>
+      </c>
+      <c r="J20" s="12">
+        <v>1</v>
+      </c>
+      <c r="K20" s="12">
+        <v>1</v>
+      </c>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R20" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T20" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="7">
+        <v>20</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="12">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12">
+        <v>1</v>
+      </c>
+      <c r="K21" s="12">
+        <v>1</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R21" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T21" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U21" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="7">
+        <v>21</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="12">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12">
+        <v>1</v>
+      </c>
+      <c r="K22" s="12">
+        <v>1</v>
+      </c>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R22" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T22" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U22" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B23" s="7">
+        <v>22</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="12">
+        <v>1</v>
+      </c>
+      <c r="J23" s="12">
+        <v>1</v>
+      </c>
+      <c r="K23" s="12">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R23" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T23" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U23" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B24" s="7">
         <v>23</v>
       </c>
-      <c r="M1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R1" t="s">
-        <v>5</v>
-      </c>
-      <c r="T1" t="s">
-        <v>6</v>
-      </c>
-      <c r="U1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V1" t="s">
-        <v>18</v>
-      </c>
-      <c r="W1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>19.388000000000002</v>
-      </c>
-      <c r="B2">
-        <v>0.59599999999999997</v>
-      </c>
-      <c r="C2">
-        <v>22362.2</v>
-      </c>
-      <c r="D2" s="3">
-        <v>618451.30000000005</v>
-      </c>
-      <c r="E2">
-        <v>0.89300000000000002</v>
-      </c>
-      <c r="F2">
-        <v>1.0660000000000001</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K2">
-        <v>0.3</v>
-      </c>
-      <c r="L2">
-        <f>K2*0.9</f>
-        <v>0.27</v>
-      </c>
-      <c r="M2" s="1">
-        <f>C2/G2</f>
-        <v>22362.2</v>
-      </c>
-      <c r="N2" s="1">
-        <f>Y2/(J2*0.85*M2)</f>
-        <v>8.0053096803737456E-3</v>
-      </c>
-      <c r="O2" s="1">
-        <f>L2^2-2*N2</f>
-        <v>5.6889380639252515E-2</v>
-      </c>
-      <c r="P2" s="4">
-        <f>(L2-SQRT(O2))/0.8</f>
-        <v>3.9356314424014611E-2</v>
-      </c>
-      <c r="Q2" s="1">
-        <f>L2-0.5*0.8*P2</f>
-        <v>0.25425747423039419</v>
-      </c>
-      <c r="R2" s="2">
-        <f>Y2/(Q2*D2)</f>
-        <v>1.3547538395357724E-4</v>
-      </c>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="4">
-        <f>((0.00038*500000)/(M2*J2*0.85*0.8))</f>
-        <v>8.9248746515447078E-2</v>
-      </c>
-      <c r="X2" s="1">
-        <f>(0.00038*500000*(L2-W2*0.5*0.8))*E2</f>
-        <v>39.753766071489643</v>
-      </c>
-      <c r="Y2" s="1">
-        <f>(I2*(A2+B2))*F2</f>
-        <v>21.302944000000004</v>
-      </c>
-      <c r="Z2" s="1">
-        <f>X2-Y2</f>
-        <v>18.45082207148964</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="G3">
-        <v>1.4</v>
-      </c>
-      <c r="H3">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="I3">
-        <v>1.4</v>
-      </c>
-      <c r="J3">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K3">
-        <v>0.3</v>
-      </c>
-      <c r="R3" s="3">
-        <v>3.8000000000000002E-4</v>
-      </c>
-      <c r="X3">
-        <v>39.79</v>
-      </c>
-      <c r="Y3">
-        <v>21.31</v>
-      </c>
-      <c r="Z3">
-        <v>18.47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="G4">
-        <v>1.4</v>
-      </c>
-      <c r="H4">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="I4">
-        <v>1.4</v>
-      </c>
-      <c r="J4">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K4">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="G5">
-        <v>1.4</v>
-      </c>
-      <c r="H5">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="I5">
-        <v>1.4</v>
-      </c>
-      <c r="J5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K5">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="G6">
-        <v>1.4</v>
-      </c>
-      <c r="H6">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="I6">
-        <v>1.4</v>
-      </c>
-      <c r="J6">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="G7">
-        <v>1.4</v>
-      </c>
-      <c r="H7">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="I7">
-        <v>1.4</v>
-      </c>
-      <c r="J7">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K7">
-        <v>0.3</v>
-      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="12">
+        <v>1</v>
+      </c>
+      <c r="J24" s="12">
+        <v>1</v>
+      </c>
+      <c r="K24" s="12">
+        <v>1</v>
+      </c>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R24" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T24" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B25" s="7">
+        <v>24</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="12">
+        <v>1</v>
+      </c>
+      <c r="J25" s="12">
+        <v>1</v>
+      </c>
+      <c r="K25" s="12">
+        <v>1</v>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R25" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T25" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U25" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B26" s="7">
+        <v>25</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="12">
+        <v>1</v>
+      </c>
+      <c r="J26" s="12">
+        <v>1</v>
+      </c>
+      <c r="K26" s="12">
+        <v>1</v>
+      </c>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R26" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T26" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U26" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B27" s="7">
+        <v>26</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="12">
+        <v>1</v>
+      </c>
+      <c r="J27" s="12">
+        <v>1</v>
+      </c>
+      <c r="K27" s="12">
+        <v>1</v>
+      </c>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R27" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T27" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U27" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="7">
+        <v>27</v>
+      </c>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="12">
+        <v>1</v>
+      </c>
+      <c r="J28" s="12">
+        <v>1</v>
+      </c>
+      <c r="K28" s="12">
+        <v>1</v>
+      </c>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R28" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T28" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U28" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="7"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="12">
+        <v>1</v>
+      </c>
+      <c r="J29" s="12">
+        <v>1</v>
+      </c>
+      <c r="K29" s="12">
+        <v>1</v>
+      </c>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="R29" s="19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="19" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T29" s="17" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U29" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="17" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+    </row>
+    <row r="33" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+    </row>
+    <row r="34" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+    </row>
+    <row r="35" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+    </row>
+    <row r="36" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+    </row>
+    <row r="37" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+    </row>
+    <row r="38" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+    </row>
+    <row r="39" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+    </row>
+    <row r="40" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+    </row>
+    <row r="41" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+    </row>
+    <row r="42" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+    </row>
+    <row r="44" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+    </row>
+    <row r="45" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+    </row>
+    <row r="46" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+    </row>
+    <row r="47" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/teste da planilha_artigo_MT.xlsx
+++ b/teste da planilha_artigo_MT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\ic_victor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE036AD-8F8A-4ACD-B681-557A8409063D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7AD424-FA3F-42C0-978F-FC3D2836178B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F469007E-D377-4415-9629-4A897BF6F5EE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F469007E-D377-4415-9629-4A897BF6F5EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>gamma_c</t>
   </si>
@@ -109,6 +109,9 @@
   <si>
     <t>1-t1</t>
   </si>
+  <si>
+    <t>FAZER GRÁFIVO</t>
+  </si>
 </sst>
 </file>
 
@@ -128,7 +131,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,6 +147,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -248,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -310,6 +319,9 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -325,6 +337,940 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.7529090113735789E-2"/>
+                  <c:y val="0.53558544765237681"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="pt-BR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Planilha1!$P$5:$P$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Planilha1!$T$5:$T$11</c:f>
+              <c:numCache>
+                <c:formatCode>0,000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>86.290729411764715</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>86.098515483361695</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>84.387743301686342</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>82.526724111575376</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80.70674633684601</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>77.186314616732304</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.042493958811278</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A4EB-41CE-9116-092F009F3D12}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="100541360"/>
+        <c:axId val="100544720"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="100541360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="110"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="100544720"/>
+        <c:crossesAt val="0"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="100544720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="100541360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8298F25E-DF9C-95AC-43B7-35309E65B7FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2564,7 +3510,9 @@
     <row r="33" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="E33" s="21" t="s">
+        <v>24</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -2893,5 +3841,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/teste da planilha_artigo_MT.xlsx
+++ b/teste da planilha_artigo_MT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\ic_victor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7AD424-FA3F-42C0-978F-FC3D2836178B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C174FF2-1BEF-4FF0-A732-51B7C244499F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F469007E-D377-4415-9629-4A897BF6F5EE}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{F469007E-D377-4415-9629-4A897BF6F5EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>gamma_c</t>
   </si>
@@ -109,9 +109,6 @@
   <si>
     <t>1-t1</t>
   </si>
-  <si>
-    <t>FAZER GRÁFIVO</t>
-  </si>
 </sst>
 </file>
 
@@ -152,7 +149,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -436,29 +433,41 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Planilha1!$P$5:$P$11</c:f>
+              <c:f>Planilha1!$P$14:$P$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
@@ -466,30 +475,42 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Planilha1!$T$5:$T$11</c:f>
+              <c:f>Planilha1!$T$14:$T$24</c:f>
               <c:numCache>
-                <c:formatCode>0,000</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>86.290729411764715</c:v>
+                  <c:v>54.449792821400379</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>86.098515483361695</c:v>
+                  <c:v>53.249001031342303</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>84.387743301686342</c:v>
+                  <c:v>52.074690534386683</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>82.526724111575376</c:v>
+                  <c:v>50.926277333465748</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>80.70674633684601</c:v>
+                  <c:v>49.803190310511795</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>77.186314616732304</c:v>
+                  <c:v>48.704870942434091</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>69.042493958811278</c:v>
+                  <c:v>47.630773023359431</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46.580362392998126</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45.553116671000481</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>44.548524997171441</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43.566087777414459</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2565,12 +2586,24 @@
       <c r="B14" s="7">
         <v>13</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D14" s="15">
+        <v>1.74594254202873</v>
+      </c>
+      <c r="E14" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F14" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G14" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H14" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I14" s="12">
         <v>1</v>
       </c>
@@ -2580,52 +2613,69 @@
       <c r="K14" s="12">
         <v>1</v>
       </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
+      <c r="L14" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M14" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N14" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O14" s="17">
         <f t="shared" si="1"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P14" s="7">
         <v>0</v>
       </c>
-      <c r="P14" s="7"/>
       <c r="Q14" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R14" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="19" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T14" s="17" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S14" s="19">
+        <f>((R14*F14)/(O14*L14*0.85*0.8))</f>
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T14" s="17">
+        <f>(R14*F14*(N14-S14*0.5*0.8))*G14*Q14</f>
+        <v>54.449792821400379</v>
       </c>
       <c r="U14" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="17" t="e">
+        <v>23.368371692274867</v>
+      </c>
+      <c r="V14" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>31.081421129125513</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="7">
         <v>14</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="C15" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D15" s="15">
+        <v>5.4438408264456104</v>
+      </c>
+      <c r="E15" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F15" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G15" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H15" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I15" s="12">
         <v>1</v>
       </c>
@@ -2635,52 +2685,69 @@
       <c r="K15" s="12">
         <v>1</v>
       </c>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
+      <c r="L15" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M15" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N15" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O15" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P15" s="7">
+        <v>10</v>
+      </c>
       <c r="Q15" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.97794680699710346</v>
       </c>
       <c r="R15" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S15" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T15" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T15" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>53.249001031342303</v>
       </c>
       <c r="U15" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="17" t="e">
+        <v>27.173249710655956</v>
+      </c>
+      <c r="V15" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>26.075751320686347</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="7">
         <v>15</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
+      <c r="C16" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D16" s="15">
+        <v>3.09726006964625</v>
+      </c>
+      <c r="E16" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F16" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G16" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H16" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I16" s="12">
         <v>1</v>
       </c>
@@ -2690,52 +2757,69 @@
       <c r="K16" s="12">
         <v>1</v>
       </c>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
+      <c r="L16" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M16" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N16" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O16" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P16" s="7">
+        <v>20</v>
+      </c>
       <c r="Q16" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.95637995731583003</v>
       </c>
       <c r="R16" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S16" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T16" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T16" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>52.074690534386683</v>
       </c>
       <c r="U16" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="17" t="e">
+        <v>24.758782666625329</v>
+      </c>
+      <c r="V16" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>27.315907867761354</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="7">
         <v>16</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
+      <c r="C17" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1.4955827923235301</v>
+      </c>
+      <c r="E17" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F17" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G17" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H17" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I17" s="12">
         <v>1</v>
       </c>
@@ -2745,52 +2829,69 @@
       <c r="K17" s="12">
         <v>1</v>
       </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
+      <c r="L17" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M17" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N17" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O17" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P17" s="7">
+        <v>30</v>
+      </c>
       <c r="Q17" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.9352887255330421</v>
       </c>
       <c r="R17" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S17" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T17" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T17" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>50.926277333465748</v>
       </c>
       <c r="U17" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="17" t="e">
+        <v>23.110769066384652</v>
+      </c>
+      <c r="V17" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>27.815508267081096</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="7">
         <v>17</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
+      <c r="C18" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D18" s="15">
+        <v>4.8334228580043002</v>
+      </c>
+      <c r="E18" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F18" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G18" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H18" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I18" s="12">
         <v>1</v>
       </c>
@@ -2800,52 +2901,69 @@
       <c r="K18" s="12">
         <v>1</v>
       </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
+      <c r="L18" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M18" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N18" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O18" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P18" s="7">
+        <v>40</v>
+      </c>
       <c r="Q18" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.91466262275542887</v>
       </c>
       <c r="R18" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S18" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T18" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T18" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>49.803190310511795</v>
       </c>
       <c r="U18" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="17" t="e">
+        <v>26.54517242688247</v>
+      </c>
+      <c r="V18" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>23.258017883629325</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B19" s="7">
         <v>18</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
+      <c r="C19" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D19" s="15">
+        <v>2.7743242095646901</v>
+      </c>
+      <c r="E19" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F19" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G19" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H19" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I19" s="12">
         <v>1</v>
       </c>
@@ -2855,52 +2973,69 @@
       <c r="K19" s="12">
         <v>1</v>
       </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
+      <c r="L19" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M19" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N19" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O19" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P19" s="7">
+        <v>50</v>
+      </c>
       <c r="Q19" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.89449139140326783</v>
       </c>
       <c r="R19" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S19" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T19" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T19" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>48.704870942434091</v>
       </c>
       <c r="U19" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="17" t="e">
+        <v>24.426504312580477</v>
+      </c>
+      <c r="V19" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>24.278366629853615</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B20" s="7">
         <v>19</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
+      <c r="C20" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1.7865536940295901</v>
+      </c>
+      <c r="E20" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F20" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G20" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H20" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I20" s="12">
         <v>1</v>
       </c>
@@ -2910,52 +3045,69 @@
       <c r="K20" s="12">
         <v>1</v>
       </c>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
+      <c r="L20" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M20" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N20" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O20" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P20" s="7">
+        <v>60</v>
+      </c>
       <c r="Q20" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.8747650001092222</v>
       </c>
       <c r="R20" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S20" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T20" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T20" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>47.630773023359431</v>
       </c>
       <c r="U20" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="17" t="e">
+        <v>23.410157719813903</v>
+      </c>
+      <c r="V20" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>24.220615303545529</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="7">
         <v>20</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
+      <c r="C21" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0.76382725652339301</v>
+      </c>
+      <c r="E21" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F21" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G21" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H21" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I21" s="12">
         <v>1</v>
       </c>
@@ -2965,52 +3117,69 @@
       <c r="K21" s="12">
         <v>1</v>
       </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
+      <c r="L21" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M21" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N21" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O21" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P21" s="7">
+        <v>70</v>
+      </c>
       <c r="Q21" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.85547363872963467</v>
       </c>
       <c r="R21" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S21" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T21" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T21" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>46.580362392998126</v>
       </c>
       <c r="U21" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="17" t="e">
+        <v>22.357843934634126</v>
+      </c>
+      <c r="V21" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>24.222518458364</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="7">
         <v>21</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
+      <c r="C22" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D22" s="15">
+        <v>7.7316970305144102</v>
+      </c>
+      <c r="E22" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F22" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G22" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H22" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I22" s="12">
         <v>1</v>
       </c>
@@ -3020,52 +3189,69 @@
       <c r="K22" s="12">
         <v>1</v>
       </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
+      <c r="L22" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M22" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N22" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O22" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P22" s="7">
+        <v>80</v>
+      </c>
       <c r="Q22" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.83660771346583995</v>
       </c>
       <c r="R22" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S22" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T22" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T22" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>45.553116671000481</v>
       </c>
       <c r="U22" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="17" t="e">
+        <v>29.527293308004619</v>
+      </c>
+      <c r="V22" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>16.025823362995862</v>
       </c>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B23" s="7">
         <v>22</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
+      <c r="C23" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D23" s="15">
+        <v>2.1755529680632799</v>
+      </c>
+      <c r="E23" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F23" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G23" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H23" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I23" s="12">
         <v>1</v>
       </c>
@@ -3075,52 +3261,69 @@
       <c r="K23" s="12">
         <v>1</v>
       </c>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
+      <c r="L23" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M23" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N23" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O23" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P23" s="7">
+        <v>90</v>
+      </c>
       <c r="Q23" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.81815784209306586</v>
       </c>
       <c r="R23" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S23" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T23" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T23" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>44.548524997171441</v>
       </c>
       <c r="U23" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="17" t="e">
+        <v>23.810410694097751</v>
+      </c>
+      <c r="V23" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>20.73811430307369</v>
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B24" s="7">
         <v>23</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
+      <c r="C24" s="15">
+        <v>20.965393057436</v>
+      </c>
+      <c r="D24" s="15">
+        <v>2.2744902970148502</v>
+      </c>
+      <c r="E24" s="13">
+        <v>21916.977462928</v>
+      </c>
+      <c r="F24" s="13">
+        <v>615489.33721737203</v>
+      </c>
+      <c r="G24" s="15">
+        <v>1.03394410027032</v>
+      </c>
+      <c r="H24" s="15">
+        <v>1.0289298746844999</v>
+      </c>
       <c r="I24" s="12">
         <v>1</v>
       </c>
@@ -3130,40 +3333,45 @@
       <c r="K24" s="12">
         <v>1</v>
       </c>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
+      <c r="L24" s="12">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M24" s="12">
+        <v>0.3</v>
+      </c>
       <c r="N24" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="O24" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="7"/>
+        <v>21916.977462928</v>
+      </c>
+      <c r="P24" s="7">
+        <v>100</v>
+      </c>
       <c r="Q24" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.80011484929455412</v>
       </c>
       <c r="R24" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="19" t="e">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="S24" s="19">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T24" s="17" t="e">
+        <v>0.1120950721293905</v>
+      </c>
+      <c r="T24" s="17">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>43.566087777414459</v>
       </c>
       <c r="U24" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="17" t="e">
+        <v>23.91221026757751</v>
+      </c>
+      <c r="V24" s="17">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>19.653877509836949</v>
       </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
@@ -3201,8 +3409,7 @@
         <v>1</v>
       </c>
       <c r="R25" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3.8000000000000002E-4</v>
       </c>
       <c r="S25" s="19" t="e">
         <f t="shared" si="3"/>
@@ -3510,9 +3717,7 @@
     <row r="33" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="21" t="s">
-        <v>24</v>
-      </c>
+      <c r="E33" s="21"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
